--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.69602580773753</v>
+        <v>9.213104193757349</v>
       </c>
       <c r="D2" t="n">
-        <v>56.79698430365269</v>
+        <v>9.229509949343562</v>
       </c>
       <c r="E2" t="n">
-        <v>16.07281355311549</v>
+        <v>2.611832202381267</v>
       </c>
       <c r="F2" t="n">
-        <v>10.76912824421172</v>
+        <v>1.749983339684404</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.13062022339327</v>
+        <v>9.121225786301407</v>
       </c>
       <c r="D3" t="n">
-        <v>55.77387035710628</v>
+        <v>9.06325393302977</v>
       </c>
       <c r="E3" t="n">
-        <v>16.07281355311549</v>
+        <v>2.611832202381267</v>
       </c>
       <c r="F3" t="n">
-        <v>10.76912824421172</v>
+        <v>1.749983339684404</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.31706295154719</v>
+        <v>6.226522729626418</v>
       </c>
       <c r="D4" t="n">
-        <v>37.96223177582398</v>
+        <v>6.168862663571397</v>
       </c>
       <c r="E4" t="n">
-        <v>16.07281355311549</v>
+        <v>2.611832202381267</v>
       </c>
       <c r="F4" t="n">
-        <v>10.76912824421172</v>
+        <v>1.749983339684404</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.28835119352595</v>
+        <v>8.334357068947968</v>
       </c>
       <c r="D5" t="n">
-        <v>50.98752133947793</v>
+        <v>8.285472217665165</v>
       </c>
       <c r="E5" t="n">
-        <v>16.07281355311549</v>
+        <v>2.611832202381267</v>
       </c>
       <c r="F5" t="n">
-        <v>10.76912824421172</v>
+        <v>1.749983339684404</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.20616373302047</v>
+        <v>4.746001606615826</v>
       </c>
       <c r="D6" t="n">
-        <v>40.19642437536765</v>
+        <v>6.531918960997243</v>
       </c>
       <c r="E6" t="n">
-        <v>16.07281355311549</v>
+        <v>2.611832202381267</v>
       </c>
       <c r="F6" t="n">
-        <v>10.76912824421172</v>
+        <v>1.749983339684404</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.23492608400799</v>
+        <v>2.963175488651298</v>
       </c>
       <c r="D7" t="n">
-        <v>18.29211975318784</v>
+        <v>2.972469459893024</v>
       </c>
       <c r="E7" t="n">
-        <v>16.07281355311549</v>
+        <v>2.611832202381267</v>
       </c>
       <c r="F7" t="n">
-        <v>10.76912824421172</v>
+        <v>1.749983339684404</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.00543414065468</v>
+        <v>3.738383047856386</v>
       </c>
       <c r="D8" t="n">
-        <v>42.76324498037835</v>
+        <v>6.949027309311482</v>
       </c>
       <c r="E8" t="n">
-        <v>16.07281355311549</v>
+        <v>2.611832202381267</v>
       </c>
       <c r="F8" t="n">
-        <v>10.76912824421172</v>
+        <v>1.749983339684404</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.61296676434253</v>
+        <v>4.324607099205661</v>
       </c>
       <c r="D9" t="n">
-        <v>50.81889882102427</v>
+        <v>8.258071058416444</v>
       </c>
       <c r="E9" t="n">
-        <v>16.07281355311549</v>
+        <v>2.611832202381267</v>
       </c>
       <c r="F9" t="n">
-        <v>10.76912824421172</v>
+        <v>1.749983339684404</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>10.30776406404415</v>
+        <v>1.675011660407175</v>
       </c>
       <c r="D10" t="n">
-        <v>50.17484089459563</v>
+        <v>8.15341164537179</v>
       </c>
       <c r="E10" t="n">
-        <v>16.07281355311549</v>
+        <v>2.611832202381267</v>
       </c>
       <c r="F10" t="n">
-        <v>10.76912824421172</v>
+        <v>1.749983339684404</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.61375009447417</v>
+        <v>2.862234390352053</v>
       </c>
       <c r="D11" t="n">
-        <v>49.2418732130116</v>
+        <v>8.001804397114386</v>
       </c>
       <c r="E11" t="n">
-        <v>16.07281355311549</v>
+        <v>2.611832202381267</v>
       </c>
       <c r="F11" t="n">
-        <v>10.76912824421172</v>
+        <v>1.749983339684404</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
